--- a/数据采集配置.xlsx
+++ b/数据采集配置.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\go-energy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E297F7-BAFB-4878-9004-B6B24C82102A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF365DBA-9780-46E7-8F49-5FC50C32885E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="配置表" sheetId="15" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">设备表!$A$1:$L$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">设备表!$A$1:$M$130</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="205">
   <si>
     <t>编号</t>
   </si>
@@ -474,18 +474,12 @@
     <t>九号配电室</t>
   </si>
   <si>
-    <t>1号挤出机</t>
-  </si>
-  <si>
     <t>192.168.40.19</t>
   </si>
   <si>
     <t>2号挤出机</t>
   </si>
   <si>
-    <t>3号挤出机</t>
-  </si>
-  <si>
     <t>4号挤出机</t>
   </si>
   <si>
@@ -501,148 +495,171 @@
     <t>8号挤出机</t>
   </si>
   <si>
+    <t>11号挤出机</t>
+  </si>
+  <si>
+    <t>14号冷却塔</t>
+  </si>
+  <si>
+    <t>192.168.59.21</t>
+  </si>
+  <si>
+    <t>15号冷却塔</t>
+  </si>
+  <si>
+    <t>192.168.59.22</t>
+  </si>
+  <si>
+    <t>7号环保设备</t>
+  </si>
+  <si>
+    <t>192.168.36.15</t>
+  </si>
+  <si>
+    <t>铜米机</t>
+  </si>
+  <si>
+    <t>1号悬臂单绞机</t>
+  </si>
+  <si>
+    <t>2号悬臂单绞机</t>
+  </si>
+  <si>
+    <t>桑普1000+1250电源1</t>
+  </si>
+  <si>
+    <t>桑普1000+1250电源2</t>
+  </si>
+  <si>
+    <t>3号成缆机</t>
+  </si>
+  <si>
+    <t>桑普1000绞线机</t>
+  </si>
+  <si>
+    <t>63号笼绞机</t>
+  </si>
+  <si>
+    <t>64号笼绞机</t>
+  </si>
+  <si>
+    <t>16号冷却塔</t>
+  </si>
+  <si>
+    <t>192.168.59.23</t>
+  </si>
+  <si>
+    <t>电子加速器</t>
+  </si>
+  <si>
+    <t>复绕机（电气值班室外）</t>
+  </si>
+  <si>
+    <t>三车间南侧照明（及办公室）</t>
+  </si>
+  <si>
+    <t>三车间北侧照明及行车电源</t>
+  </si>
+  <si>
+    <t>动力站</t>
+  </si>
+  <si>
+    <t>18号冷却塔</t>
+  </si>
+  <si>
+    <t>192.168.59.24</t>
+  </si>
+  <si>
+    <t>研发楼</t>
+  </si>
+  <si>
+    <t>1号变压器</t>
+  </si>
+  <si>
+    <t>2号变压器</t>
+  </si>
+  <si>
+    <t>3号变压器</t>
+  </si>
+  <si>
+    <t>4号变压器</t>
+  </si>
+  <si>
+    <t>5号变压器</t>
+  </si>
+  <si>
+    <t>6号变压器</t>
+  </si>
+  <si>
+    <t>7号变压器</t>
+  </si>
+  <si>
+    <t>8号变压器</t>
+  </si>
+  <si>
+    <t>9号变压器</t>
+  </si>
+  <si>
+    <t>十号配电室</t>
+  </si>
+  <si>
+    <t>10号变压器</t>
+  </si>
+  <si>
+    <t>USER</t>
+  </si>
+  <si>
+    <t>jldgxcx</t>
+  </si>
+  <si>
+    <t>PASSWORD</t>
+  </si>
+  <si>
+    <t>Jldg123654.</t>
+  </si>
+  <si>
+    <t>HOST</t>
+  </si>
+  <si>
+    <t>xs.jldg.com</t>
+  </si>
+  <si>
+    <t>DATABASE</t>
+  </si>
+  <si>
+    <t>192.168.40.19</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>二车间</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>七号配电室</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>二车间冷感机</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>二车间空压机</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>192.168.40.17</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>e20250529</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
     <t>9号挤出机</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>10号挤出机</t>
-  </si>
-  <si>
-    <t>11号挤出机</t>
-  </si>
-  <si>
-    <t>14号冷却塔</t>
-  </si>
-  <si>
-    <t>192.168.59.21</t>
-  </si>
-  <si>
-    <t>15号冷却塔</t>
-  </si>
-  <si>
-    <t>192.168.59.22</t>
-  </si>
-  <si>
-    <t>7号环保设备</t>
-  </si>
-  <si>
-    <t>192.168.36.15</t>
-  </si>
-  <si>
-    <t>铜米机</t>
-  </si>
-  <si>
-    <t>1号悬臂单绞机</t>
-  </si>
-  <si>
-    <t>2号悬臂单绞机</t>
-  </si>
-  <si>
-    <t>桑普1000+1250电源1</t>
-  </si>
-  <si>
-    <t>桑普1000+1250电源2</t>
-  </si>
-  <si>
-    <t>3号成缆机</t>
-  </si>
-  <si>
-    <t>桑普1000绞线机</t>
-  </si>
-  <si>
-    <t>63号笼绞机</t>
-  </si>
-  <si>
-    <t>64号笼绞机</t>
-  </si>
-  <si>
-    <t>16号冷却塔</t>
-  </si>
-  <si>
-    <t>192.168.59.23</t>
-  </si>
-  <si>
-    <t>电子加速器</t>
-  </si>
-  <si>
-    <t>复绕机（电气值班室外）</t>
-  </si>
-  <si>
-    <t>三车间南侧照明（及办公室）</t>
-  </si>
-  <si>
-    <t>三车间北侧照明及行车电源</t>
-  </si>
-  <si>
-    <t>动力站</t>
-  </si>
-  <si>
-    <t>18号冷却塔</t>
-  </si>
-  <si>
-    <t>192.168.59.24</t>
-  </si>
-  <si>
-    <t>研发楼</t>
-  </si>
-  <si>
-    <t>1号变压器</t>
-  </si>
-  <si>
-    <t>2号变压器</t>
-  </si>
-  <si>
-    <t>3号变压器</t>
-  </si>
-  <si>
-    <t>4号变压器</t>
-  </si>
-  <si>
-    <t>5号变压器</t>
-  </si>
-  <si>
-    <t>6号变压器</t>
-  </si>
-  <si>
-    <t>7号变压器</t>
-  </si>
-  <si>
-    <t>8号变压器</t>
-  </si>
-  <si>
-    <t>9号变压器</t>
-  </si>
-  <si>
-    <t>十号配电室</t>
-  </si>
-  <si>
-    <t>10号变压器</t>
-  </si>
-  <si>
-    <t>USER</t>
-  </si>
-  <si>
-    <t>jldgxcx</t>
-  </si>
-  <si>
-    <t>PASSWORD</t>
-  </si>
-  <si>
-    <t>Jldg123654.</t>
-  </si>
-  <si>
-    <t>HOST</t>
-  </si>
-  <si>
-    <t>xs.jldg.com</t>
-  </si>
-  <si>
-    <t>DATABASE</t>
-  </si>
-  <si>
-    <t>energy</t>
-  </si>
-  <si>
-    <t>192.168.40.19</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -787,7 +804,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -823,6 +840,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1131,6 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -2168,7 +2192,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8">
         <v>25</v>
       </c>
@@ -2209,7 +2233,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A27" s="8">
         <v>26</v>
       </c>
@@ -2250,7 +2274,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8">
         <v>27</v>
       </c>
@@ -2291,7 +2315,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A29" s="8">
         <v>28</v>
       </c>
@@ -2332,7 +2356,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8">
         <v>29</v>
       </c>
@@ -3398,7 +3422,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A56" s="8">
         <v>55</v>
       </c>
@@ -3439,7 +3463,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A57" s="8">
         <v>56</v>
       </c>
@@ -3480,7 +3504,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A58" s="8">
         <v>57</v>
       </c>
@@ -3521,7 +3545,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A59" s="8">
         <v>58</v>
       </c>
@@ -3685,7 +3709,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A63" s="8">
         <v>62</v>
       </c>
@@ -3849,7 +3873,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -3890,7 +3914,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -3931,7 +3955,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -3972,7 +3996,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -4013,7 +4037,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -4054,7 +4078,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A72" s="8">
         <v>71</v>
       </c>
@@ -4300,7 +4324,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A78" s="8">
         <v>77</v>
       </c>
@@ -4341,7 +4365,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -4382,7 +4406,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A80" s="8">
         <v>79</v>
       </c>
@@ -4423,7 +4447,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -4755,26 +4779,26 @@
       <c r="A89" s="5">
         <v>96</v>
       </c>
-      <c r="B89" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>141</v>
+      <c r="B89" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>199</v>
       </c>
       <c r="E89" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F89" s="5" t="s">
-        <v>101</v>
+      <c r="F89" s="11" t="s">
+        <v>201</v>
       </c>
       <c r="G89" s="5">
         <v>502</v>
       </c>
       <c r="H89" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I89" s="5">
         <v>18</v>
@@ -4796,26 +4820,26 @@
       <c r="A90" s="5">
         <v>97</v>
       </c>
-      <c r="B90" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>142</v>
+      <c r="B90" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>200</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F90" s="5" t="s">
-        <v>134</v>
+      <c r="F90" s="11" t="s">
+        <v>201</v>
       </c>
       <c r="G90" s="5">
         <v>502</v>
       </c>
       <c r="H90" s="5">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I90" s="5">
         <v>18</v>
@@ -4838,25 +4862,25 @@
         <v>98</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="G91" s="5">
         <v>502</v>
       </c>
       <c r="H91" s="5">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="I91" s="5">
         <v>18</v>
@@ -4879,25 +4903,25 @@
         <v>99</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="G92" s="5">
         <v>502</v>
       </c>
       <c r="H92" s="5">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="I92" s="5">
         <v>18</v>
@@ -4925,20 +4949,20 @@
       <c r="C93" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D93" s="5" t="s">
-        <v>148</v>
+      <c r="D93" s="13" t="s">
+        <v>203</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G93" s="5">
         <v>502</v>
       </c>
       <c r="H93" s="5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I93" s="5">
         <v>18</v>
@@ -4966,20 +4990,20 @@
       <c r="C94" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D94" s="8" t="s">
-        <v>149</v>
+      <c r="D94" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G94" s="5">
         <v>502</v>
       </c>
       <c r="H94" s="5">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I94" s="5">
         <v>18</v>
@@ -5007,20 +5031,20 @@
       <c r="C95" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D95" s="8" t="s">
-        <v>150</v>
+      <c r="D95" s="11" t="s">
+        <v>204</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G95" s="5">
         <v>502</v>
       </c>
       <c r="H95" s="5">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I95" s="5">
         <v>18</v>
@@ -5049,19 +5073,19 @@
         <v>144</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G96" s="5">
         <v>502</v>
       </c>
       <c r="H96" s="5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I96" s="5">
         <v>18</v>
@@ -5089,20 +5113,20 @@
       <c r="C97" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D97" s="5" t="s">
-        <v>152</v>
+      <c r="D97" s="8" t="s">
+        <v>148</v>
       </c>
       <c r="E97" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G97" s="5">
         <v>502</v>
       </c>
       <c r="H97" s="5">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="I97" s="5">
         <v>18</v>
@@ -5131,19 +5155,19 @@
         <v>144</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G98" s="5">
         <v>502</v>
       </c>
       <c r="H98" s="5">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I98" s="5">
         <v>18</v>
@@ -5172,19 +5196,19 @@
         <v>144</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E99" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G99" s="5">
         <v>502</v>
       </c>
       <c r="H99" s="5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I99" s="5">
         <v>18</v>
@@ -5213,19 +5237,19 @@
         <v>144</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E100" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G100" s="5">
         <v>502</v>
       </c>
       <c r="H100" s="5">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I100" s="5">
         <v>18</v>
@@ -5245,7 +5269,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A101" s="5">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>143</v>
@@ -5254,13 +5278,13 @@
         <v>144</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E101" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G101" s="5">
         <v>502</v>
@@ -5284,9 +5308,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A102" s="8">
-        <v>110</v>
+    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A102" s="5">
+        <v>111</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>143</v>
@@ -5295,13 +5319,13 @@
         <v>47</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E102" s="5" t="s">
         <v>49</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G102" s="5">
         <v>102</v>
@@ -5325,9 +5349,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A103" s="8">
-        <v>111</v>
+    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="5">
+        <v>112</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>143</v>
@@ -5336,13 +5360,13 @@
         <v>47</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E103" s="5" t="s">
         <v>49</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G103" s="5">
         <v>102</v>
@@ -5366,9 +5390,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A104" s="8">
-        <v>112</v>
+    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A104" s="5">
+        <v>113</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>143</v>
@@ -5377,13 +5401,13 @@
         <v>47</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>49</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G104" s="5">
         <v>102</v>
@@ -5408,8 +5432,8 @@
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A105" s="8">
-        <v>113</v>
+      <c r="A105" s="5">
+        <v>114</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>143</v>
@@ -5418,13 +5442,13 @@
         <v>144</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E105" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G105" s="5">
         <v>502</v>
@@ -5449,8 +5473,8 @@
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A106" s="8">
-        <v>114</v>
+      <c r="A106" s="5">
+        <v>115</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>143</v>
@@ -5459,13 +5483,13 @@
         <v>144</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E106" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G106" s="5">
         <v>502</v>
@@ -5490,8 +5514,8 @@
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A107" s="8">
-        <v>115</v>
+      <c r="A107" s="5">
+        <v>116</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>143</v>
@@ -5500,13 +5524,13 @@
         <v>144</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E107" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G107" s="5">
         <v>502</v>
@@ -5531,8 +5555,8 @@
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A108" s="8">
-        <v>116</v>
+      <c r="A108" s="5">
+        <v>117</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>143</v>
@@ -5541,13 +5565,13 @@
         <v>144</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E108" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G108" s="5">
         <v>502</v>
@@ -5572,8 +5596,8 @@
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A109" s="8">
-        <v>117</v>
+      <c r="A109" s="5">
+        <v>118</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>143</v>
@@ -5582,13 +5606,13 @@
         <v>144</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G109" s="5">
         <v>502</v>
@@ -5613,8 +5637,8 @@
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A110" s="8">
-        <v>118</v>
+      <c r="A110" s="5">
+        <v>119</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>143</v>
@@ -5623,13 +5647,13 @@
         <v>144</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G110" s="5">
         <v>502</v>
@@ -5654,8 +5678,8 @@
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A111" s="8">
-        <v>119</v>
+      <c r="A111" s="5">
+        <v>120</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>143</v>
@@ -5664,13 +5688,13 @@
         <v>144</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E111" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G111" s="5">
         <v>502</v>
@@ -5695,8 +5719,8 @@
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A112" s="8">
-        <v>120</v>
+      <c r="A112" s="5">
+        <v>121</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>143</v>
@@ -5705,13 +5729,13 @@
         <v>144</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E112" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G112" s="5">
         <v>502</v>
@@ -5736,8 +5760,8 @@
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A113" s="8">
-        <v>121</v>
+      <c r="A113" s="5">
+        <v>122</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>143</v>
@@ -5746,13 +5770,13 @@
         <v>144</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G113" s="5">
         <v>502</v>
@@ -5776,8 +5800,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A114" s="8">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A114" s="5">
         <v>123</v>
       </c>
       <c r="B114" s="5" t="s">
@@ -5787,13 +5811,13 @@
         <v>47</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E114" s="5" t="s">
         <v>49</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G114" s="5">
         <v>102</v>
@@ -5818,7 +5842,7 @@
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A115" s="8">
+      <c r="A115" s="5">
         <v>124</v>
       </c>
       <c r="B115" s="5" t="s">
@@ -5828,13 +5852,13 @@
         <v>144</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E115" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G115" s="5">
         <v>502</v>
@@ -5859,7 +5883,7 @@
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A116" s="8">
+      <c r="A116" s="5">
         <v>125</v>
       </c>
       <c r="B116" s="5" t="s">
@@ -5869,13 +5893,13 @@
         <v>144</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E116" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G116" s="5">
         <v>502</v>
@@ -5900,7 +5924,7 @@
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A117" s="8">
+      <c r="A117" s="5">
         <v>126</v>
       </c>
       <c r="B117" s="5" t="s">
@@ -5910,13 +5934,13 @@
         <v>144</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E117" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G117" s="5">
         <v>502</v>
@@ -5941,7 +5965,7 @@
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A118" s="8">
+      <c r="A118" s="5">
         <v>127</v>
       </c>
       <c r="B118" s="5" t="s">
@@ -5951,13 +5975,13 @@
         <v>144</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G118" s="5">
         <v>502</v>
@@ -5981,24 +6005,24 @@
         <v>19</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A119" s="8">
-        <v>130</v>
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A119" s="5">
+        <v>128</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>47</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E119" s="5" t="s">
         <v>49</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G119" s="5">
         <v>102</v>
@@ -6024,7 +6048,7 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A120" s="5">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>143</v>
@@ -6033,13 +6057,13 @@
         <v>144</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E120" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G120" s="5">
         <v>502</v>
@@ -6064,8 +6088,8 @@
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A121" s="10">
-        <v>143</v>
+      <c r="A121" s="5">
+        <v>130</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>13</v>
@@ -6074,7 +6098,7 @@
         <v>37</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E121" s="5" t="s">
         <v>16</v>
@@ -6105,8 +6129,8 @@
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A122" s="10">
-        <v>144</v>
+      <c r="A122" s="5">
+        <v>131</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>13</v>
@@ -6115,7 +6139,7 @@
         <v>27</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E122" s="5" t="s">
         <v>16</v>
@@ -6146,8 +6170,8 @@
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A123" s="10">
-        <v>145</v>
+      <c r="A123" s="5">
+        <v>132</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>13</v>
@@ -6156,7 +6180,7 @@
         <v>14</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>16</v>
@@ -6187,8 +6211,8 @@
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A124" s="10">
-        <v>146</v>
+      <c r="A124" s="5">
+        <v>133</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>13</v>
@@ -6197,7 +6221,7 @@
         <v>76</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>16</v>
@@ -6228,8 +6252,8 @@
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A125" s="10">
-        <v>147</v>
+      <c r="A125" s="5">
+        <v>134</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>13</v>
@@ -6238,7 +6262,7 @@
         <v>62</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E125" s="5" t="s">
         <v>16</v>
@@ -6269,8 +6293,8 @@
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A126" s="10">
-        <v>148</v>
+      <c r="A126" s="5">
+        <v>135</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>98</v>
@@ -6279,7 +6303,7 @@
         <v>99</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E126" s="5" t="s">
         <v>16</v>
@@ -6310,8 +6334,8 @@
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A127" s="10">
-        <v>149</v>
+      <c r="A127" s="5">
+        <v>136</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>98</v>
@@ -6320,7 +6344,7 @@
         <v>103</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E127" s="5" t="s">
         <v>16</v>
@@ -6351,8 +6375,8 @@
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A128" s="10">
-        <v>150</v>
+      <c r="A128" s="5">
+        <v>137</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>98</v>
@@ -6361,7 +6385,7 @@
         <v>132</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E128" s="5" t="s">
         <v>16</v>
@@ -6392,8 +6416,8 @@
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A129" s="10">
-        <v>151</v>
+      <c r="A129" s="5">
+        <v>138</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>143</v>
@@ -6402,13 +6426,13 @@
         <v>144</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E129" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G129" s="5">
         <v>502</v>
@@ -6433,23 +6457,23 @@
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A130" s="10">
-        <v>152</v>
+      <c r="A130" s="5">
+        <v>139</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>143</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E130" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G130" s="5">
         <v>502</v>
@@ -6474,6 +6498,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M130" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="18"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J129">
     <sortCondition ref="A2:A129"/>
   </sortState>
@@ -6494,26 +6525,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.15">
@@ -6526,10 +6557,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
